--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486411_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486411_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5262</v>
+        <v>3.2451</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2371</v>
+        <v>1.7094</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2891</v>
+        <v>1.5357</v>
       </c>
       <c r="G2" t="n">
         <v>2.5128</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3341</v>
+        <v>-0.6153</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0274</v>
+        <v>-0.5552</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3067</v>
+        <v>-0.0601</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4712</v>
+        <v>0.9796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2376</v>
+        <v>-0.1628</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2336</v>
+        <v>1.1425</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1829</v>
+        <v>0.7897</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0609</v>
+        <v>1.6758</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2438</v>
+        <v>-0.8861</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1877</v>
+        <v>1.1014</v>
       </c>
       <c r="K3" t="n">
-        <v>0.073</v>
+        <v>1.0981</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>0.0032</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0049</v>
+        <v>-0.3117</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1339</v>
+        <v>0.5776</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1291</v>
+        <v>-0.8893</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4318</v>
+        <v>-0.1238</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9421</v>
+        <v>-0.1766</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4897</v>
+        <v>0.0529</v>
       </c>
       <c r="V3" t="n">
-        <v>0.074</v>
+        <v>-0.1213</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-0.1213</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9409</v>
+        <v>0.7473</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0719</v>
+        <v>1.6934</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.131</v>
+        <v>-0.946</v>
       </c>
       <c r="G4" t="n">
         <v>0.0501</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1831</v>
+        <v>-0.3767</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2572</v>
+        <v>-0.1214</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4403</v>
+        <v>-0.2554</v>
       </c>
       <c r="V4" t="n">
         <v>0.6389</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2521</v>
+        <v>0.715</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0136</v>
+        <v>-0.3645</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2658</v>
+        <v>1.0795</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7897</v>
+        <v>0.1829</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6758</v>
+        <v>-0.0609</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8861</v>
+        <v>0.2438</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1014</v>
+        <v>0.1877</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0981</v>
+        <v>0.073</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0032</v>
+        <v>0.1147</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3117</v>
+        <v>-0.0049</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5776</v>
+        <v>-0.1339</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8893</v>
+        <v>0.1291</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.6757</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0274</v>
+        <v>0.3401</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1762</v>
+        <v>0.3356</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1213</v>
+        <v>0.074</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1213</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1609</v>
+        <v>-1.8026</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5152</v>
+        <v>0.627</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6761</v>
+        <v>-2.4295</v>
       </c>
       <c r="G6" t="n">
         <v>-2.6692</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7381</v>
+        <v>-0.3797</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0036</v>
+        <v>0.1154</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7417</v>
+        <v>-0.4951</v>
       </c>
       <c r="V6" t="n">
         <v>2.3339</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9256</v>
+        <v>-2.7</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4854</v>
+        <v>-2.0132</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4402</v>
+        <v>-0.6868</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2902</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.418</v>
+        <v>-0.1923</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8099</v>
+        <v>-0.3377</v>
       </c>
       <c r="U7" t="n">
-        <v>0.392</v>
+        <v>0.1454</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. RICHARDSON</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6421</v>
+        <v>-3.637</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5547</v>
+        <v>-2.2929</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0874</v>
+        <v>-1.3441</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.545</v>
+        <v>-3.0419</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5384</v>
+        <v>-1.2562</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.0066</v>
+        <v>-1.7858</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.5393</v>
+        <v>-0.8417</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.6903</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.9037</v>
+        <v>-0.1514</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0057</v>
+        <v>-2.2003</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.5659</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1029</v>
+        <v>-1.6344</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4761</v>
+        <v>-0.6375</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1454</v>
+        <v>-0.4062</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3307</v>
+        <v>-0.2313</v>
       </c>
       <c r="V8" t="n">
-        <v>0.074</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>T. RICHARDSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2257</v>
+        <v>-3.7038</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6967</v>
+        <v>-2.5547</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.529</v>
+        <v>-1.1491</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0419</v>
+        <v>-4.545</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2562</v>
+        <v>-0.5384</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7858</v>
+        <v>-4.0066</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8417</v>
+        <v>-3.5393</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6903</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1514</v>
+        <v>-2.9037</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2003</v>
+        <v>-1.0057</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5659</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6344</v>
+        <v>-1.1029</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2262</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8099</v>
+        <v>-0.1454</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4163</v>
+        <v>-0.3924</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>0.074</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8639</v>
+        <v>-5.4775</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.312</v>
+        <v>-2.8023</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5519</v>
+        <v>-2.6752</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3364</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0702</v>
+        <v>-0.6838</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2692</v>
+        <v>-0.2211</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3394</v>
+        <v>-0.4627</v>
       </c>
       <c r="V10" t="n">
         <v>0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2199</v>
+        <v>-6.529</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3584</v>
+        <v>-2.5134</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8615</v>
+        <v>-4.0156</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9327</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3203</v>
+        <v>0.0111</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2091</v>
+        <v>0.0541</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1111</v>
+        <v>-0.043</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3899</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.8477</v>
+        <v>-18.1629</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.359</v>
+        <v>-8.673999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.4886</v>
+        <v>-9.488599999999998</v>
       </c>
       <c r="G12" t="n">
         <v>-16.2799</v>
@@ -1390,10 +1390,10 @@
         <v>11.9625</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.544999999999999</v>
+        <v>-2.8601</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1388</v>
+        <v>-1.454</v>
       </c>
       <c r="U12" t="n">
         <v>-1.4061</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1636</v>
+        <v>9.401199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7665</v>
+        <v>5.9784</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3971</v>
+        <v>3.4228</v>
       </c>
       <c r="G13" t="n">
         <v>3.9009</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>3.72</v>
+        <v>1.9576</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0643</v>
+        <v>1.2762</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6556</v>
+        <v>0.6813</v>
       </c>
       <c r="V13" t="n">
         <v>2.4552</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4395</v>
+        <v>7.5557</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6794</v>
+        <v>5.4617</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7601</v>
+        <v>2.094</v>
       </c>
       <c r="G14" t="n">
         <v>6.7328</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7708</v>
+        <v>0.3455</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6044</v>
+        <v>0.1779</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1663</v>
+        <v>0.1676</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2618</v>
+        <v>4.5304</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6684</v>
+        <v>2.0036</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5935</v>
+        <v>2.5267</v>
       </c>
       <c r="G15" t="n">
         <v>3.9154</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5411</v>
+        <v>0.8096</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1214</v>
+        <v>0.2139</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6625</v>
+        <v>0.5957</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4997</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9881</v>
+        <v>2.6606</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3853</v>
+        <v>2.1697</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6028</v>
+        <v>0.491</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0974</v>
+        <v>2.0171</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2743</v>
+        <v>1.3868</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1769</v>
+        <v>0.6303</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9707</v>
+        <v>1.8929</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8942</v>
+        <v>1.2227</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0765</v>
+        <v>0.6702</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1267</v>
+        <v>0.1242</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3801</v>
+        <v>0.1641</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2534</v>
+        <v>-0.0399</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0207</v>
+        <v>0.2085</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4146</v>
+        <v>0.2343</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6061</v>
+        <v>-0.0258</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9142</v>
+        <v>2.5797</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3873</v>
+        <v>1.1618</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5269</v>
+        <v>1.4179</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0171</v>
+        <v>1.0974</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3868</v>
+        <v>1.2743</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6303</v>
+        <v>-0.1769</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8929</v>
+        <v>0.9707</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2227</v>
+        <v>0.8942</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6702</v>
+        <v>0.0765</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1242</v>
+        <v>0.1267</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1641</v>
+        <v>0.3801</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0399</v>
+        <v>-0.2534</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5379</v>
+        <v>0.6123</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.548</v>
+        <v>0.1911</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0101</v>
+        <v>0.4212</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8335</v>
+        <v>1.7796</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4533</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3801</v>
+        <v>1.1027</v>
       </c>
       <c r="G18" t="n">
         <v>0.159</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5445</v>
+        <v>0.4906</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9555</v>
+        <v>0.678</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.8279</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2863</v>
+        <v>-0.6216</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.571</v>
+        <v>-0.2063</v>
       </c>
       <c r="G19" t="n">
         <v>1.4522</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3854</v>
+        <v>0.4149</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6117</v>
+        <v>0.2764</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2263</v>
+        <v>0.1385</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9619</v>
+        <v>-1.3901</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0331</v>
+        <v>-1.1347</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0712</v>
+        <v>-0.2554</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0483</v>
+        <v>-0.8452</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8999</v>
+        <v>-1.9465</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9483</v>
+        <v>1.1013</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1939</v>
+        <v>-0.92</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2465</v>
+        <v>-1.3806</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0527</v>
+        <v>0.4606</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2422</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3466</v>
+        <v>-0.5659</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1044</v>
+        <v>0.6407</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.0875</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2073</v>
+        <v>0.0201</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1406</v>
+        <v>-0.2572</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0667</v>
+        <v>0.2773</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0028</v>
+        <v>-2.0313</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.47</v>
+        <v>-2.2566</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0.2253</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8452</v>
+        <v>0.0483</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9465</v>
+        <v>-0.8999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1013</v>
+        <v>0.9483</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.92</v>
+        <v>-0.1939</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3806</v>
+        <v>-1.2465</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4606</v>
+        <v>1.0527</v>
       </c>
       <c r="M21" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.2422</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5659</v>
+        <v>0.3466</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6407</v>
+        <v>-0.1044</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5926</v>
+        <v>0.1379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5924</v>
+        <v>-0.0829</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0001</v>
+        <v>0.2208</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9309</v>
+        <v>-4.665</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.062</v>
+        <v>-3.9503</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8688</v>
+        <v>-0.7147</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1979</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9728</v>
+        <v>-0.7069</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4248</v>
+        <v>-0.2707</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>18.8477</v>
+        <v>19.5929</v>
       </c>
       <c r="E23" t="n">
-        <v>9.488800000000001</v>
+        <v>9.488900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>9.3591</v>
+        <v>10.104</v>
       </c>
       <c r="G23" t="n">
         <v>16.28</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3350000000000002</v>
+        <v>0.3350000000000006</v>
       </c>
       <c r="I23" t="n">
         <v>15.9451</v>
@@ -2248,22 +2248,22 @@
         <v>13.0503</v>
       </c>
       <c r="S23" t="n">
-        <v>3.544900000000001</v>
+        <v>4.2901</v>
       </c>
       <c r="T23" t="n">
         <v>1.406</v>
       </c>
       <c r="U23" t="n">
-        <v>2.139</v>
+        <v>2.8839</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0646</v>
       </c>
       <c r="W23" t="n">
-        <v>6.9958</v>
+        <v>6.995799999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.060600000000001</v>
+        <v>-9.060599999999999</v>
       </c>
     </row>
   </sheetData>
